--- a/APLOS/MeetingReport.xlsx
+++ b/APLOS/MeetingReport.xlsx
@@ -1263,7 +1263,7 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0">
     <oddFooter>&amp;L&amp;"Times New Roman"&amp;06Printed By: Md  Sulaiman
-Print Date &amp;&amp; Time: 07-Mar-2022 3:47 PM&amp;R&amp;"Times New Roman"&amp;06Page &amp;P of &amp;N</oddFooter>
+Print Date &amp;&amp; Time: 07-Mar-2022 5:57 PM&amp;R&amp;"Times New Roman"&amp;06Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <extLst/>
 </worksheet>
